--- a/textbook_examples/mod01_sort_filter.xlsx
+++ b/textbook_examples/mod01_sort_filter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://usaskca1-my.sharepoint.com/personal/pjs998_usask_ca/Documents/Teaching/261/2026/textbook_261/textbook_examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="8_{00F64A42-DA52-D941-B03F-5C3FDB9D63FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{320D0EB7-995F-BB4E-B802-6F1A58B9CB73}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{00F64A42-DA52-D941-B03F-5C3FDB9D63FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91278CD9-6369-1C46-8492-90803B182E47}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="24320" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
